--- a/order_forms/043_grocery_delivery_form--order_forms.xlsx
+++ b/order_forms/043_grocery_delivery_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'product_1'}</t>
+          <t>product_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Product 1'}</t>
+          <t>Product 1</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'product_2'}</t>
+          <t>product_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Product 2'}</t>
+          <t>Product 2</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'product_3'}</t>
+          <t>product_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Product 3'}</t>
+          <t>Product 3</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'stripe'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Stripe'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'credit_card_number'}</t>
+          <t>credit_card_number</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Credit Card Number'}</t>
+          <t>Credit Card Number</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'expiration_date'}</t>
+          <t>expiration_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Expiration Date'}</t>
+          <t>Expiration Date</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cvv'}</t>
+          <t>cvv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'CVV'}</t>
+          <t>CVV</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'card_type'}</t>
+          <t>card_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Card Type'}</t>
+          <t>Card Type</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'bank_name'}</t>
+          <t>bank_name</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Bank Name'}</t>
+          <t>Bank Name</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'routing_number'}</t>
+          <t>routing_number</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Routing Number'}</t>
+          <t>Routing Number</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'refunded'}</t>
+          <t>refunded</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Refunded'}</t>
+          <t>Refunded</t>
         </is>
       </c>
     </row>
